--- a/Project gestion/Dépenses.xlsx
+++ b/Project gestion/Dépenses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univorleansfr-my.sharepoint.com/personal/o22302770_campus_univ-orleans_fr/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thibm\OneDrive\Documents\GitHub\CFR2027\Project gestion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A368B4-88E0-4E62-829F-54350B7AADF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBA64AF-67D1-44CD-99A8-0F537E93028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="3" xr2:uid="{DC506655-D796-47EE-BDAC-EDB6EB12EC7A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="3" xr2:uid="{DC506655-D796-47EE-BDAC-EDB6EB12EC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Général" sheetId="1" r:id="rId1"/>
@@ -20,28 +20,17 @@
     <sheet name="Pompe" sheetId="5" r:id="rId5"/>
     <sheet name="Feuil1" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
   <si>
     <t>Produit</t>
   </si>
@@ -257,16 +246,50 @@
   </si>
   <si>
     <t>FIT0801</t>
+  </si>
+  <si>
+    <t>Moteur</t>
+  </si>
+  <si>
+    <t>370 FIT0801</t>
+  </si>
+  <si>
+    <t>Vide min (kpa)</t>
+  </si>
+  <si>
+    <t>Vide min requis = -30kpa</t>
+  </si>
+  <si>
+    <t>Débit (L/min)</t>
+  </si>
+  <si>
+    <t>Diamètre de sortie (mm)</t>
+  </si>
+  <si>
+    <t>AliExpress</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.us/item/3256805770721534.html</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005006476509817.html?spm=a2g0o.productlist.main.4.58d8267f2absbs&amp;aem_p4p_detail=202610210127336588276842480480000094386&amp;algo_pvid=2c9c043c-d203-40e4-bcbd-8442561367db&amp;algo_exp_id=2c9c043c-d203-40e4-bcbd-8442561367db-3&amp;pdp_ext_f=%7B"order"%3A"12"%2C"eval"%3A"1"%2C"fromPage"%3A"search"%7D&amp;pdp_npi=6%40dis%21EUR%215.19%215.19%21%21%215.69%215.69%21%400b15834e17925712533892786e0ea1%2112000037342014469%21sea%21FR%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Afda5f202%3Bm03_new_user%3A-29895&amp;curPageLogUid=RhHnMSGfmdep&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006476509817%7C_p_origin_prod%3A&amp;search_p4p_id=202610210127336588276842480480000094386_1</t>
+  </si>
+  <si>
+    <t>VN-2707PM</t>
+  </si>
+  <si>
+    <t>370C-22155</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,7 +319,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,8 +344,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -610,6 +639,273 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -617,7 +913,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -697,6 +993,44 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -716,7 +1050,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1013,15 +1347,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6A0A22-9DBC-4F42-9960-59990673E4FB}">
   <dimension ref="B1:G13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="5" max="5" width="60.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1039,7 +1373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1053,7 +1387,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,7 +1401,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,7 +1417,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,7 +1435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1117,7 +1451,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2">
@@ -1129,7 +1463,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1145,7 +1479,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1161,7 +1495,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1177,7 +1511,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1193,7 +1527,7 @@
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1209,7 +1543,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -1231,25 +1565,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013231D0-FD6A-4B80-9270-6B4969006B71}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="62.5703125" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="62.5546875" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>21</v>
       </c>
@@ -1278,7 +1612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1310,7 +1644,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1321,14 +1655,14 @@
       <c r="I5" s="11"/>
       <c r="J5" s="15"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="16"/>
       <c r="F6" s="15"/>
       <c r="G6" s="14"/>
       <c r="I6" s="11"/>
       <c r="J6" s="15"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="17"/>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
@@ -1344,23 +1678,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4746E5-8DEC-4FBC-AFFD-A05EEF34C996}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="14"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="32.88671875" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="14"/>
     <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" s="18" t="s">
         <v>21</v>
       </c>
@@ -1389,7 +1723,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>33</v>
       </c>
@@ -1425,7 +1759,7 @@
         <v>95.36999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="21" t="s">
         <v>36</v>
       </c>
@@ -1457,7 +1791,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
@@ -1489,7 +1823,7 @@
         <v>33.96</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1">
+    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="27" t="s">
         <v>40</v>
       </c>
@@ -1518,7 +1852,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="16"/>
     </row>
   </sheetData>
@@ -1533,19 +1867,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B7EAC6-6B63-41E7-8C21-49F258C20125}">
-  <dimension ref="B2:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="14"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="40" t="s">
         <v>22</v>
       </c>
@@ -1573,49 +1909,56 @@
       <c r="J2" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="44" t="s">
         <v>49</v>
       </c>
       <c r="M2" s="40" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="36" t="s">
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="55">
         <v>6</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="55">
         <v>3.6</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="55">
         <v>2.7</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="55">
         <v>300</v>
       </c>
-      <c r="I3" s="38">
+      <c r="I3" s="56">
         <v>21.5</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="39">
+      <c r="K3" s="58"/>
+      <c r="L3" s="66">
         <v>8</v>
       </c>
-      <c r="M3" s="39" t="s">
+      <c r="M3" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B4" s="30" t="s">
         <v>50</v>
       </c>
@@ -1637,20 +1980,23 @@
       <c r="H4" s="28">
         <v>100</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="50">
         <v>21.5</v>
       </c>
       <c r="J4" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="63">
         <v>5</v>
       </c>
-      <c r="M4" s="31" t="s">
+      <c r="M4" s="61" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B5" s="30" t="s">
         <v>50</v>
       </c>
@@ -1672,20 +2018,23 @@
       <c r="H5" s="28">
         <v>210</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="50">
         <v>21.5</v>
       </c>
       <c r="J5" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="63">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="61" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B6" s="30" t="s">
         <v>50</v>
       </c>
@@ -1707,20 +2056,23 @@
       <c r="H6" s="28">
         <v>251</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="50">
         <v>26.3</v>
       </c>
       <c r="J6" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="63">
         <v>0</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="M6" s="61" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B7" s="30" t="s">
         <v>50</v>
       </c>
@@ -1742,20 +2094,23 @@
       <c r="H7" s="28">
         <v>83</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="50">
         <v>26.3</v>
       </c>
       <c r="J7" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="63">
         <v>0</v>
       </c>
-      <c r="M7" s="31" t="s">
+      <c r="M7" s="61" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B8" s="30" t="s">
         <v>50</v>
       </c>
@@ -1777,24 +2132,27 @@
       <c r="H8" s="28">
         <v>160</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="50">
         <v>8.9</v>
       </c>
       <c r="J8" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="63">
         <v>5</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="61" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B9" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="68">
         <v>4755</v>
       </c>
       <c r="D9" s="28">
@@ -1812,20 +2170,23 @@
       <c r="H9" s="28">
         <v>100</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="50">
         <v>69.5</v>
       </c>
       <c r="J9" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="63">
         <v>0</v>
       </c>
-      <c r="M9" s="31" t="s">
+      <c r="M9" s="61" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B10" s="30" t="s">
         <v>34</v>
       </c>
@@ -1847,20 +2208,23 @@
       <c r="H10" s="28">
         <v>620</v>
       </c>
-      <c r="I10" s="29">
-        <v>9.49</v>
+      <c r="I10" s="50">
+        <v>9.99</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="63">
         <v>10</v>
       </c>
-      <c r="M10" s="31" t="s">
+      <c r="M10" s="61" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="40" t="s">
+        <v>72</v>
+      </c>
       <c r="B11" s="32" t="s">
         <v>34</v>
       </c>
@@ -1882,18 +2246,241 @@
       <c r="H11" s="33">
         <v>282</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="51">
         <v>6.29</v>
       </c>
       <c r="J11" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="64">
         <v>8</v>
       </c>
-      <c r="M11" s="35" t="s">
+      <c r="M11" s="62" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14"/>
+      <c r="L14" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="74">
+        <v>5</v>
+      </c>
+      <c r="E15" s="74">
+        <f>-58</f>
+        <v>-58</v>
+      </c>
+      <c r="F15" s="74">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G15" s="74">
+        <v>4.3</v>
+      </c>
+      <c r="H15" s="75">
+        <v>6.9</v>
+      </c>
+      <c r="I15"/>
+      <c r="L15" s="74">
+        <v>8</v>
+      </c>
+      <c r="M15" s="76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="H16" s="52">
+        <v>5.19</v>
+      </c>
+      <c r="I16"/>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="46" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="48">
+        <v>6</v>
+      </c>
+      <c r="E17" s="48">
+        <v>-60</v>
+      </c>
+      <c r="F17" s="48">
+        <v>3</v>
+      </c>
+      <c r="G17" s="48">
+        <v>4.3</v>
+      </c>
+      <c r="H17" s="53">
+        <v>3.69</v>
+      </c>
+      <c r="I17"/>
+      <c r="L17" s="48">
+        <v>5</v>
+      </c>
+      <c r="M17" s="49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="59"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="59"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="59"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="59"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1906,6 +2493,8 @@
     <hyperlink ref="M9" r:id="rId7" xr:uid="{E6BBF59F-DBC8-4046-86CB-49443B35CF9B}"/>
     <hyperlink ref="M10" r:id="rId8" display="https://fr.aliexpress.com/item/4001314473291.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.5.462dxyYKxyYKhE&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40050.354490.0&amp;scm_id=1007.40050.354490.0&amp;scm-url=1007.40050.354490.0&amp;pvid=1e5f46a4-c870-485f-b0e4-fa0461695485&amp;_t=gps-id%3ApcDetailTopMoreOtherSeller%2Cscm-url%3A1007.40050.354490.0%2Cpvid%3A1e5f46a4-c870-485f-b0e4-fa0461695485%2Ctpp_buckets%3A668%232846%238107%231934&amp;pdp_ext_f=%7B%22order%22%3A%22610%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22sceneId%22%3A%2230050%22%2C%22fromPage%22%3A%22recommend%22%7D&amp;pdp_npi=6%40dis%21EUR%219.99%219.99%21%21%2110.95%2110.95%21%400b0fe08917915498353555025e0ead%2112000050913315715%21rec%21FR%21%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ae75bf42%3Bm03_new_user%3A-29895&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A%7Cx_object_id%3A4001314473291%7C_p_origin_prod%3A" xr:uid="{32D347F8-CBFA-4534-A3C5-D875FD89B188}"/>
     <hyperlink ref="M11" r:id="rId9" display="https://fr.aliexpress.com/item/1005009095909930.html?spm=a2g0o.productlist.main.13.395a7385lAZkPe&amp;algo_pvid=435ecf1f-7460-4324-a019-353c5a35ef82&amp;algo_exp_id=435ecf1f-7460-4324-a019-353c5a35ef82-12&amp;pdp_ext_f=%7B%22order%22%3A%2273%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%216.86%216.29%21%21%2150.29%2146.08%21%400b8848bf17921449700828002e105b%2112000047894628827%21sea%21FR%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ae75bf42%3Bm03_new_user%3A-29895&amp;curPageLogUid=pIGJIPpt6fA2&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009095909930%7C_p_origin_prod%3A" xr:uid="{84701D29-9455-4A52-9578-201F9718F8E9}"/>
+    <hyperlink ref="M16" r:id="rId10" display="https://fr.aliexpress.com/item/32890830349.html" xr:uid="{9F642F9F-30D7-4C5A-9960-17F7441342ED}"/>
+    <hyperlink ref="M17" r:id="rId11" xr:uid="{D84B001A-2858-438C-A0F0-B9B555B02BC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1914,16 +2503,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336ACE9E-6ABE-4B5C-BDB2-0AF761B4C4D2}">
   <dimension ref="B2:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="40" t="s">
         <v>22</v>
       </c>
@@ -1958,7 +2547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="36" t="s">
         <v>50</v>
       </c>
@@ -1991,7 +2580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="30"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
@@ -2004,7 +2593,7 @@
       <c r="L4" s="31"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="30"/>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
@@ -2017,7 +2606,7 @@
       <c r="L5" s="31"/>
       <c r="M5" s="31"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="30"/>
       <c r="C6" s="28"/>
       <c r="D6" s="28"/>
@@ -2030,7 +2619,7 @@
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="30"/>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
@@ -2043,7 +2632,7 @@
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="30"/>
       <c r="C8" s="28"/>
       <c r="D8" s="28"/>
@@ -2056,7 +2645,7 @@
       <c r="L8" s="31"/>
       <c r="M8" s="31"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="30"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
@@ -2069,7 +2658,7 @@
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="30"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
@@ -2082,7 +2671,7 @@
       <c r="L10" s="31"/>
       <c r="M10" s="31"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2106,13 +2695,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34FF1E22-DE99-4BB0-96B9-4C0CBBCB3B3F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007934F44BA1E0F24F9930540811A2EDB6" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="63da83260db1d72dc3600b2d6132f719">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2a37fc6c6d9ad226a4d0af2afcddd6e5" ns3:_="">
     <xsd:import namespace="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
@@ -2262,31 +2868,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2630977E-B0CF-45C9-B99D-25EACCA74DA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9B7E90-EAE5-48E9-9092-492A01032B48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CDEBE5B-8EDA-4F49-8F8E-C6674C0EDC90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CDEBE5B-8EDA-4F49-8F8E-C6674C0EDC90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9B7E90-EAE5-48E9-9092-492A01032B48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2630977E-B0CF-45C9-B99D-25EACCA74DA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>